--- a/docs/团队角色清单.xlsx
+++ b/docs/团队角色清单.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="106">
   <si>
     <t>G05 设备台账与测点资产目录 —— 团队角色清单（请组员填写黄色列）</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>卢思雨</t>
+  </si>
+  <si>
+    <t>Jasonlu555</t>
   </si>
   <si>
     <t>C-01</t>
@@ -364,7 +367,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,13 +424,6 @@
       <color rgb="FF262626"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -931,148 +927,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1652,7 +1648,9 @@
       <c r="H7" s="13">
         <v>2025460782</v>
       </c>
-      <c r="I7" s="12"/>
+      <c r="I7" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
       <c r="L7" s="14"/>
@@ -1664,32 +1662,32 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:17">
       <c r="A8" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="10">
         <f>角色速览!F6</f>
         <v>5</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H8" s="16">
         <v>2025460063</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -1702,32 +1700,32 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:17">
       <c r="A9" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="10">
         <f>角色速览!F7</f>
         <v>4</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H9" s="13">
         <v>2025461082</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J9" s="14"/>
       <c r="K9" s="14"/>
@@ -1740,32 +1738,32 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:17">
       <c r="A10" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E10" s="10">
         <f>角色速览!F8</f>
         <v>6</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H10" s="16">
         <v>2025460094</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
@@ -1778,32 +1776,32 @@
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:17">
       <c r="A11" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11" s="10">
         <f>角色速览!F9</f>
         <v>9</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H11" s="13">
         <v>2025460581</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
@@ -1816,32 +1814,32 @@
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:17">
       <c r="A12" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="10">
         <f>角色速览!F10</f>
         <v>2</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H12" s="16">
         <v>2025461305</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="14"/>
@@ -1854,32 +1852,32 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:17">
       <c r="A13" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" s="10">
         <f>角色速览!F11</f>
         <v>4</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H13" s="13">
         <v>2025460987</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="14"/>
@@ -1931,15 +1929,15 @@
   <sheetData>
     <row r="2" ht="17.5" spans="2:3">
       <c r="B2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="2:3">
       <c r="B4" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="2:3">
@@ -1947,23 +1945,23 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="2:3">
       <c r="B6" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="2:3">
       <c r="B7" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1" spans="2:3">
@@ -1971,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1" spans="2:3">
@@ -1979,31 +1977,31 @@
         <v>16</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1" spans="2:3">
       <c r="B10" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1" spans="2:3">
       <c r="B11" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1" spans="2:3">
       <c r="B12" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2029,7 +2027,7 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2040,19 +2038,19 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2075,7 +2073,7 @@
         <v>51</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2098,7 +2096,7 @@
         <v>11</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2121,21 +2119,21 @@
         <v>6</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3">
         <v>3</v>
@@ -2144,21 +2142,21 @@
         <v>5</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="3">
         <v>4</v>
@@ -2167,21 +2165,21 @@
         <v>4</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" s="3">
         <v>4</v>
@@ -2190,21 +2188,21 @@
         <v>6</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3">
         <v>4</v>
@@ -2213,21 +2211,21 @@
         <v>9</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3">
         <v>4</v>
@@ -2236,21 +2234,21 @@
         <v>2</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E11" s="3">
         <v>5</v>
@@ -2259,7 +2257,7 @@
         <v>4</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
